--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118597475</v>
+        <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>88971</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,48 +810,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>363</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavaria rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Dalman:Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N om Lumpen, skogsbilväg, Upl</t>
+          <t>Lumpen N, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627412</v>
+        <v>627509</v>
       </c>
       <c r="R3" t="n">
-        <v>6649511</v>
+        <v>6649542</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,12 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,27 +894,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118597475</t>
+          <t>https://artportalen.se/Sighting/137285968</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69962910</v>
+        <v>118597475</v>
       </c>
       <c r="B4" t="n">
-        <v>93136</v>
+        <v>88971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,46 +922,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2075</v>
+        <v>363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Rosenfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Clavaria rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>Dalman:Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Styggkärret, intill NR, Upl</t>
+          <t>N om Lumpen, skogsbilväg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>627412</v>
       </c>
       <c r="R4" t="n">
-        <v>6649548</v>
+        <v>6649511</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,17 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1995-06-01</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1995-06-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4 dm2 på naken ved på avbruten stamdel, omkr. ca. 120 cm, från ekhögstubbe, omkr. 264 cm.</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,88 +1003,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Skogsek</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Naken ved på avbruten stamdel från ekhögstubbe. # Skogsek</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Karin Martinsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69962910</t>
+          <t>https://artportalen.se/Sighting/118597475</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74681475</v>
+        <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>57141</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Styggkärret, intill NR, Upl</t>
+          <t>Lumpen N, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627413</v>
+        <v>627524</v>
       </c>
       <c r="R5" t="n">
-        <v>6649508</v>
+        <v>6649539</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,17 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1995-06-27</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1995-06-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 tupp vid en vägkant.</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,27 +1119,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74681475</t>
+          <t>https://artportalen.se/Sighting/137285972</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79136113</v>
+        <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>5435</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,54 +1147,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101859</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalvingad blombock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Strangalia attenuata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lumpen, Upl</t>
+          <t>Lumpen N, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627508</v>
+        <v>627556</v>
       </c>
       <c r="R6" t="n">
-        <v>6649462</v>
+        <v>6649624</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,17 +1201,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På strätta i vägkanten</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,34 +1225,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79136113</t>
+          <t>https://artportalen.se/Sighting/137285982</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94814167</v>
+        <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>5435</v>
+        <v>92580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,44 +1259,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101859</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalvingad blombock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Strangalia attenuata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Lumpen N, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627413</v>
+        <v>627503</v>
       </c>
       <c r="R7" t="n">
-        <v>6649506</v>
+        <v>6649495</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,22 +1313,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,76 +1343,74 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Freddy Persson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Freddy Persson, David Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94814167</t>
+          <t>https://artportalen.se/Sighting/137285974</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118597481</v>
+        <v>69962910</v>
       </c>
       <c r="B8" t="n">
-        <v>89079</v>
+        <v>93136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>239209</v>
+        <v>2075</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N om Lumpen, skogsbilväg, Upl</t>
+          <t>Styggkärret, intill NR, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>627412</v>
       </c>
       <c r="R8" t="n">
-        <v>6649511</v>
+        <v>6649548</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,12 +1434,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>1995-06-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>1995-06-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 dm2 på naken ved på avbruten stamdel, omkr. ca. 120 cm, från ekhögstubbe, omkr. 264 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,22 +1455,3735 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Naken ved på avbruten stamdel från ekhögstubbe. # Skogsek</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/69962910</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137285979</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96697</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627555</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6649594</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285979</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137285980</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96697</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>627550</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6649596</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285980</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137285987</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96697</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>627543</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6649647</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285987</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137285964</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92111</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>627483</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6649560</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285964</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137285966</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92111</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627469</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6649549</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285966</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137285989</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92111</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>627446</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6649563</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285989</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137285988</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>627505</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6649618</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285988</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137285963</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>627492</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6649559</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285963</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137285967</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>627486</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6649539</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285967</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137285981</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>627548</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6649603</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285981</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>74681475</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Styggkärret, intill NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>627413</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6649508</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>1995-06-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1995-06-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 tupp vid en vägkant.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74681475</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137285971</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>627524</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6649539</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285971</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137285955</v>
+      </c>
+      <c r="B21" t="n">
+        <v>44225</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>627449</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6649551</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285955</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137285973</v>
+      </c>
+      <c r="B22" t="n">
+        <v>44225</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>627520</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6649509</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285973</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>79136113</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5435</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lumpen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>627508</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6649462</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På strätta i vägkanten</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79136113</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>94814167</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5435</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>627413</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6649506</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Freddy Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Freddy Persson, David Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94814167</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137285956</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>627501</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6649572</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285956</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137285969</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>627525</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6649543</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285969</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137285976</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>627483</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6649586</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285976</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137285957</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>627534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6649568</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285957</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137285958</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>627531</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6649576</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285958</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137285959</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>627533</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6649575</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285959</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137285960</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>627527</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6649573</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285960</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137285961</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>627521</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6649572</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285961</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137285962</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>627483</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6649560</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285962</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137285965</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>627478</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6649555</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285965</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137285978</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>627533</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6649581</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285978</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137285984</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>627572</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6649637</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285984</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137285985</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>627572</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6649647</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285985</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137285986</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>627560</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6649649</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137285986</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118597481</v>
+      </c>
+      <c r="B39" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>N om Lumpen, skogsbilväg, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>627412</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6649511</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Karin Martinsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/118597481</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137288519</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92540</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lumpen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>627434</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6649534</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137288519</t>
         </is>
       </c>
     </row>
@@ -1518,6 +5196,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137285988</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137285963</v>
       </c>
       <c r="B16" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137285967</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>137285981</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137285971</v>
       </c>
       <c r="B20" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>137285955</v>
       </c>
       <c r="B21" t="n">
-        <v>44225</v>
+        <v>44235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137285973</v>
       </c>
       <c r="B22" t="n">
-        <v>44225</v>
+        <v>44235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>137285956</v>
       </c>
       <c r="B25" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>137285969</v>
       </c>
       <c r="B26" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>137285976</v>
       </c>
       <c r="B27" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92540</v>
+        <v>92550</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137285988</v>
       </c>
       <c r="B15" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137285963</v>
       </c>
       <c r="B16" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137285967</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>137285981</v>
       </c>
       <c r="B18" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>137285955</v>
       </c>
       <c r="B21" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137285973</v>
       </c>
       <c r="B22" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92551</v>
+        <v>92554</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137285988</v>
       </c>
       <c r="B15" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137285963</v>
       </c>
       <c r="B16" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137285967</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>137285981</v>
       </c>
       <c r="B18" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92556</v>
+        <v>92561</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137285988</v>
       </c>
       <c r="B15" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92561</v>
+        <v>92573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137285988</v>
       </c>
       <c r="B15" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137285988</v>
       </c>
       <c r="B15" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41955-2026 artfynd.xlsx
+++ b/artfynd/A 41955-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>137285968</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137285972</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137285982</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137285974</v>
       </c>
       <c r="B7" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137285979</v>
       </c>
       <c r="B9" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137285980</v>
       </c>
       <c r="B10" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137285987</v>
       </c>
       <c r="B11" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137285964</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137285966</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137285989</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137285988</v>
       </c>
       <c r="B15" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137285963</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137285967</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>137285981</v>
       </c>
       <c r="B18" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>137285957</v>
       </c>
       <c r="B28" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137285958</v>
       </c>
       <c r="B29" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>137285959</v>
       </c>
       <c r="B30" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>137285960</v>
       </c>
       <c r="B31" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137285961</v>
       </c>
       <c r="B32" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>137285962</v>
       </c>
       <c r="B33" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137285965</v>
       </c>
       <c r="B34" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137285978</v>
       </c>
       <c r="B35" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137285984</v>
       </c>
       <c r="B36" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>137285985</v>
       </c>
       <c r="B37" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137285986</v>
       </c>
       <c r="B38" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>137288519</v>
       </c>
       <c r="B40" t="n">
-        <v>92577</v>
+        <v>92581</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
